--- a/samples/ss_byoli_ingest.xlsx
+++ b/samples/ss_byoli_ingest.xlsx
@@ -632,31 +632,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -703,15 +693,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -727,7 +713,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -774,15 +759,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -798,7 +779,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -827,35 +807,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>4 seksi bus (A/B/C/D) + Kopel A, Kopel B; 60 MVA</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -884,35 +855,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -941,35 +903,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>3x60 MVA + 50 MVAR</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -998,23 +951,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1030,7 +976,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1059,23 +1004,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1091,7 +1029,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1120,17 +1057,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>3x60 MVA; batas ke Subsistem Pedan 1,2</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1146,13 +1077,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1181,23 +1110,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1213,7 +1135,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1242,19 +1163,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1270,7 +1183,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1299,31 +1211,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1352,31 +1254,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1483,7 +1375,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>SUTT Boyolali - Banaran</t>
@@ -1504,7 +1395,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -1518,8 +1408,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1536,13 +1424,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT Boyolali - Bendono</t>
@@ -1563,7 +1449,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -1577,8 +1462,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1595,7 +1478,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1626,7 +1508,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -1640,8 +1521,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1658,7 +1537,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1689,7 +1567,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -1703,8 +1580,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1721,7 +1596,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1752,7 +1626,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1766,8 +1639,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1784,13 +1655,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Bendono - Jajar</t>
@@ -1811,7 +1680,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1825,8 +1693,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1843,13 +1709,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Boyolali - Jajar</t>
@@ -1870,7 +1734,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1884,8 +1747,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1902,7 +1763,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1933,7 +1793,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1947,8 +1806,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1965,13 +1822,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Outlet PLTA Jelok</t>
@@ -1992,7 +1847,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -2006,8 +1860,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2024,13 +1876,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Outlet PLTA Timo</t>
@@ -2051,7 +1901,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -2065,8 +1914,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2083,7 +1930,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2193,7 +2039,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2237,7 +2082,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2316,12 +2160,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.Pekerjaan padam IBT hanya bisa dilaksanakan saat beban rendah. 2.OLS Adaptif IBT Boyolali 1,2</t>
+          <t>1. Pekerjaan padam IBT hanya bisa dilaksanakan saat beban rendah. 2. OLS Adaptif IBT Boyolali 1,2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026 ). Informasi terupdate COD Desember 2027. 2. Usulan Pembangunan SUTT 150kV Boyolali- Masaran / SUTT 150kV Boyolali Gondangrejo. Usulan 2027</t>
+          <t>Jangka Pendek: 1. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026 ). Informasi terupdate COD Desember 2027. 2. Usulan Pembangunan SUTT 150kV Boyolali- Masaran / SUTT 150kV Boyolali Gondangrejo. Usulan 2027</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2185,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Terdapat potensi overload IBT-3 Ungaran ketika Subsistem IBT 1, 2 GITET Boyolali Looping dengan Subsistem Tanjungjati.(N-1 SUTET Ungaran-Boyolali)</t>
+          <t>[N-1] Terdapat potensi overload IBT-3 Ungaran ketika Subsistem IBT 1, 2 GITET Boyolali Looping dengan Subsistem Tanjungjati.(N-1 SUTET Ungaran -Boyolali)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2351,12 +2195,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.Pekerjaan padam IBT hanya bisa dilaksanakan saat beban rendah. 2.Melakukan pengaturan pembangkit pada PLTU Tanjungjati</t>
+          <t>1. Pekerjaan padam IBT hanya bisa dilaksanakan saat beban rendah. 2. Melakukan pengaturan pembangkit pada PLTU Tanjungjati</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan SUTET Ungaran-Boyolali-Pedan sirkit 2 (RUPTL 2025-2034 COD 2025) informasi terupdate COD Desember 2027. 2.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027</t>
+          <t>Jangka Pendek: 1. Pembangunan SUTET Ungaran-Boyolali-Pedan sirkit 2 (RUPTL 2025-2034 COD 2025) informasi terupdate COD Desember 2027. 2. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2230,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.Pekerjaan hanya bisa dilakukan saat beban rendah 2.Pemasangan OLS SUTT Boyolali-Mojosongo</t>
+          <t>1. Pekerjaan hanya bisa dilakukan saat beban rendah 2. Pemasangan OLS SUTT Boyolali-Mojosongo</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2421,12 +2265,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT Ungaran-Jelok 2.Pekerjaan padam IBT hanya bisa dilaksanakan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT Ungaran-Jelok 2. Pekerjaan padam IBT hanya bisa dilaksanakan saat beban rendah</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan SUTET Ungaran-Boyolali-Pedan sirkit 2 (RUPTL 2025-2034 COD 2025) informasi terupdate COD Desember 2027. 2.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027. Jangka Menengah: 3.Rekonduktoring SUTT 150 kV Ungaran-Jelok- Sangrahan menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2030). Update UIT: Akan terkontrak 2026 COD 2027</t>
+          <t>Jangka Pendek: 1. Pembangunan SUTET Ungaran-Boyolali-Pedan sirkit 2 (RUPTL 2025-2034 COD 2025) informasi terupdate COD Desember 2027. 2. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027. Jangka Menengah: 3. Rekonduktoring SUTT 150 kV Ungaran-Jelok- Sangrahan menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2030). Update UIT: Akan terkontrak 2026 COD 2027</t>
         </is>
       </c>
     </row>
